--- a/docs/d/105/inyear.xlsx
+++ b/docs/d/105/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 58 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 57 clubs short</t>
         </is>
       </c>
     </row>
@@ -2815,13 +2815,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>4</v>
       </c>
       <c r="W21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" s="10" t="n">
         <v>7</v>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3648,8 +3648,8 @@
       <c r="T29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U29" s="9" t="n">
-        <v>0</v>
+      <c r="U29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V29" s="9" t="n">
         <v>3</v>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4643,8 +4643,8 @@
       <c r="S39" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T39" s="9" t="n">
-        <v>0</v>
+      <c r="T39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U39" s="9" t="n">
         <v>0</v>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q47" s="10" t="n">
         <v>2</v>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8757,8 +8757,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q95" s="9" t="n">
         <v>0</v>
@@ -12806,7 +12806,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -12905,7 +12905,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13202,7 +13202,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>

--- a/docs/d/105/inyear.xlsx
+++ b/docs/d/105/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,11 @@
       <c r="AB9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -5288,7 +5292,11 @@
       <c r="AB45" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC45" s="4" t="inlineStr"/>
+      <c r="AC45" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -5805,7 +5813,11 @@
       <c r="AB50" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC50" s="4" t="inlineStr"/>
+      <c r="AC50" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -6217,7 +6229,11 @@
       <c r="AB54" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC54" s="4" t="inlineStr"/>
+      <c r="AC54" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -6940,7 +6956,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7041,7 +7061,11 @@
       <c r="AB62" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC62" s="4" t="inlineStr"/>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -7849,7 +7873,11 @@
       <c r="AB70" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC70" s="4" t="inlineStr"/>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -9493,7 +9521,11 @@
       <c r="AB86" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC86" s="4" t="inlineStr"/>
+      <c r="AC86" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -9804,7 +9836,11 @@
       <c r="AB89" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -10414,7 +10450,11 @@
       <c r="AB95" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC95" s="4" t="inlineStr"/>
+      <c r="AC95" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -12042,7 +12082,11 @@
       <c r="AB111" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC111" s="4" t="inlineStr"/>
+      <c r="AC111" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">

--- a/docs/d/105/inyear.xlsx
+++ b/docs/d/105/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 57 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 56 clubs short</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2854,8 +2854,8 @@
       <c r="R21" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S21" s="9" t="n">
-        <v>1</v>
+      <c r="S21" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T21" s="10" t="n">
         <v>1</v>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3640,8 +3640,8 @@
       <c r="P29" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" s="9" t="n">
-        <v>1</v>
+      <c r="Q29" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R29" s="9" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3865,8 +3865,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5370,8 +5370,8 @@
       <c r="S46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T46" s="9" t="n">
-        <v>0</v>
+      <c r="T46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U46" s="9" t="n">
         <v>0</v>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5437,13 +5437,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5463,8 +5463,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P47" s="9" t="n">
-        <v>3</v>
+      <c r="P47" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q47" s="10" t="n">
         <v>2</v>
@@ -5472,8 +5472,8 @@
       <c r="R47" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S47" s="9" t="n">
-        <v>1</v>
+      <c r="S47" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T47" s="10" t="n">
         <v>1</v>
@@ -5484,8 +5484,8 @@
       <c r="V47" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W47" s="9" t="n">
-        <v>2</v>
+      <c r="W47" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X47" s="10" t="n">
         <v>7</v>
@@ -8115,13 +8115,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -10985,7 +10985,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11035,10 +11035,10 @@
         <v>0</v>
       </c>
       <c r="S101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U101" s="9" t="n">
         <v>0</v>
@@ -12817,7 +12817,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -12850,13 +12850,13 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -12883,13 +12883,13 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -12982,7 +12982,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -13015,7 +13015,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -13444,7 +13444,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>

--- a/docs/d/105/inyear.xlsx
+++ b/docs/d/105/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 56 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 37 clubs short</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1338,8 +1338,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="P9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="9" t="n">
         <v>0</v>
@@ -1625,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" s="9" t="n">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1851,8 +1851,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1952,8 +1952,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2053,8 +2053,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2675,8 +2675,8 @@
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>0</v>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2974,8 +2974,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -3059,7 +3059,7 @@
         <v>1</v>
       </c>
       <c r="U23" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V23" s="9" t="n">
         <v>2</v>
@@ -3172,8 +3172,8 @@
       <c r="Y24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="9" t="n">
-        <v>0</v>
+      <c r="Z24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA24" s="9" t="n">
         <v>0</v>
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3469,8 +3469,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3667,8 +3667,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4007,13 +4007,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4063,8 +4063,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5254,13 +5254,13 @@
         </is>
       </c>
       <c r="P45" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q45" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="Q45" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" s="10" t="n">
         <v>2</v>
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5373,8 +5373,8 @@
       <c r="T46" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U46" s="9" t="n">
-        <v>0</v>
+      <c r="U46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V46" s="9" t="n">
         <v>3</v>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5464,13 +5464,13 @@
         </is>
       </c>
       <c r="P47" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q47" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R47" s="9" t="n">
-        <v>1</v>
+      <c r="R47" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S47" s="10" t="n">
         <v>2</v>
@@ -5479,7 +5479,7 @@
         <v>1</v>
       </c>
       <c r="U47" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V47" s="10" t="n">
         <v>4</v>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5542,13 +5542,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5586,11 +5586,11 @@
       <c r="U48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="9" t="n">
-        <v>0</v>
+      <c r="V48" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>7</v>
@@ -5598,8 +5598,8 @@
       <c r="Y48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" s="9" t="n">
-        <v>0</v>
+      <c r="Z48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA48" s="10" t="n">
         <v>1</v>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5647,17 +5647,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
@@ -5691,11 +5691,11 @@
       <c r="U49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V49" s="9" t="n">
-        <v>2</v>
+      <c r="V49" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X49" s="10" t="n">
         <v>5</v>
@@ -5703,8 +5703,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="9" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6325,8 +6325,8 @@
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="9" t="n">
-        <v>0</v>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6636,8 +6636,8 @@
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
@@ -7303,13 +7303,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>4</v>
       </c>
       <c r="W65" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X65" s="10" t="n">
         <v>5</v>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8243,16 +8243,16 @@
         </is>
       </c>
       <c r="P74" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q74" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="Q74" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S74" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T74" s="9" t="n">
         <v>0</v>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9171,8 +9171,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P83" s="9" t="n">
-        <v>3</v>
+      <c r="P83" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q83" s="9" t="n">
         <v>0</v>
@@ -9201,8 +9201,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -9351,13 +9351,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9603,7 +9603,7 @@
         <v>1</v>
       </c>
       <c r="U87" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V87" s="10" t="n">
         <v>4</v>
@@ -9722,8 +9722,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="9" t="n">
         <v>0</v>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9771,13 +9771,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9815,11 +9815,11 @@
       <c r="U89" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>3</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>7</v>
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10235,8 +10235,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -10371,7 +10371,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10385,13 +10385,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T95" s="10" t="n">
         <v>1</v>
@@ -10429,11 +10429,11 @@
       <c r="U95" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V95" s="9" t="n">
-        <v>3</v>
+      <c r="V95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>7</v>
@@ -11389,7 +11389,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11441,8 +11441,8 @@
       <c r="S105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T105" s="9" t="n">
-        <v>0</v>
+      <c r="T105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U105" s="9" t="n">
         <v>0</v>
@@ -11459,8 +11459,8 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -12481,8 +12481,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="9" t="n">
         <v>0</v>
@@ -12718,7 +12718,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -12751,7 +12751,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -12784,7 +12784,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -12817,7 +12817,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -12850,7 +12850,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>2.67</v>
+        <v>3.33</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -12883,7 +12883,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -12982,7 +12982,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -13015,7 +13015,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -13030,7 +13030,7 @@
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -13048,7 +13048,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13081,7 +13081,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13213,7 +13213,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -13279,7 +13279,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13345,7 +13345,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13378,7 +13378,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>

--- a/docs/d/105/inyear.xlsx
+++ b/docs/d/105/inyear.xlsx
@@ -103,8 +103,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 37 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -883,7 +883,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -967,20 +967,20 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M3" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -988,7 +988,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1012,7 +1012,7 @@
         <v>1</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1072,20 +1072,20 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M4" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1093,7 +1093,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1117,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1177,20 +1177,20 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="M5" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1282,20 +1282,20 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="M6" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1303,7 +1303,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1326,8 +1326,8 @@
       <c r="U6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="9" t="n">
-        <v>3</v>
+      <c r="V6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1383,20 +1383,20 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
+        <v>-9</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="M7" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1404,7 +1404,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1488,20 +1488,20 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="M8" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1509,7 +1509,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1533,7 +1533,7 @@
         <v>1</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1589,20 +1589,20 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="M9" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1610,7 +1610,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1634,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1694,20 +1694,20 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
+        <v>-12</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1715,7 +1715,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1803,12 +1803,12 @@
       <c r="K11" s="4" t="n">
         <v>-8</v>
       </c>
-      <c r="L11" s="8" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1816,7 +1816,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1825,7 +1825,7 @@
         <v>1</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>0</v>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1896,20 +1896,20 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1917,7 +1917,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1997,20 +1997,20 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -2018,7 +2018,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -2123,7 +2123,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2207,20 +2207,20 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -2228,7 +2228,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2308,20 +2308,20 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -2329,7 +2329,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2409,20 +2409,20 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -2430,7 +2430,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2514,20 +2514,20 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -2535,7 +2535,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2543,8 +2543,8 @@
       <c r="P18" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Q18" s="9" t="n">
-        <v>1</v>
+      <c r="Q18" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
@@ -2619,20 +2619,20 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2640,7 +2640,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2720,20 +2720,20 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -2741,7 +2741,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" s="9" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2819,20 +2819,20 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5</v>
+        <v>-17</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2840,7 +2840,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2918,20 +2918,20 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2939,7 +2939,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2954,7 +2954,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T22" s="9" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3017,20 +3017,20 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2</v>
+        <v>-14</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -3038,7 +3038,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3061,11 +3061,11 @@
       <c r="U23" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>2</v>
+      <c r="V23" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>7</v>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3116,55 +3116,55 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K24" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W24" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M24" s="7" t="n">
-        <v>46387</v>
-      </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O24" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W24" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>7</v>
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3215,20 +3215,20 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="M25" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -3236,7 +3236,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3259,11 +3259,11 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>0</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>7</v>
@@ -3314,20 +3314,20 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>7</v>
+        <v>-8</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M26" s="7" t="n">
+      <c r="M26" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -3335,7 +3335,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3413,20 +3413,20 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3458,7 +3458,7 @@
         <v>1</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3512,20 +3512,20 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="M28" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3533,7 +3533,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3611,20 +3611,20 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="M29" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3632,7 +3632,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3655,8 +3655,8 @@
       <c r="U29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V29" s="9" t="n">
-        <v>3</v>
+      <c r="V29" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3710,20 +3710,20 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M30" s="7" t="n">
+      <c r="M30" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -3731,7 +3731,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O30" s="8" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3809,20 +3809,20 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3830,7 +3830,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O31" s="8" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3853,11 +3853,11 @@
       <c r="U31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="9" t="n">
-        <v>0</v>
+      <c r="V31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>4</v>
@@ -3908,20 +3908,20 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="M32" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3929,7 +3929,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O32" s="8" t="inlineStr">
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4007,20 +4007,20 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="M33" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -4028,7 +4028,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O33" s="8" t="inlineStr">
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4119,7 +4119,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M34" s="7" t="n">
+      <c r="M34" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -4127,7 +4127,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O34" s="8" t="inlineStr">
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4147,8 +4147,8 @@
       <c r="T34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U34" s="9" t="n">
-        <v>0</v>
+      <c r="U34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V34" s="9" t="n">
         <v>0</v>
@@ -4205,20 +4205,20 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M35" s="7" t="n">
+      <c r="M35" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -4226,7 +4226,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O35" s="8" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4306,20 +4306,20 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M36" s="7" t="n">
+      <c r="M36" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -4327,7 +4327,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O36" s="8" t="inlineStr">
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4407,20 +4407,20 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M37" s="7" t="n">
+      <c r="M37" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -4428,7 +4428,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O37" s="8" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4508,20 +4508,20 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M38" s="7" t="n">
+      <c r="M38" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -4529,7 +4529,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O38" s="8" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4609,20 +4609,20 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="M39" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -4630,13 +4630,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O39" s="8" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>0</v>
@@ -4710,20 +4710,20 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M40" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -4731,7 +4731,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O40" s="8" t="inlineStr">
+      <c r="O40" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4815,20 +4815,20 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M41" s="7" t="n">
+      <c r="M41" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4836,13 +4836,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O41" s="8" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P41" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q41" s="9" t="n">
         <v>0</v>
@@ -4853,14 +4853,14 @@
       <c r="S41" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T41" s="9" t="n">
-        <v>0</v>
+      <c r="T41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4920,20 +4920,20 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M42" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4941,7 +4941,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O42" s="8" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5033,12 +5033,12 @@
       <c r="K43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="8" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M43" s="7" t="n">
+      <c r="M43" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -5046,7 +5046,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5126,20 +5126,20 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M44" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -5147,7 +5147,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O44" s="8" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5170,11 +5170,11 @@
       <c r="U44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" s="9" t="n">
-        <v>0</v>
+      <c r="V44" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W44" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X44" s="10" t="n">
         <v>6</v>
@@ -5227,20 +5227,20 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M45" s="7" t="n">
+      <c r="M45" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -5248,7 +5248,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O45" s="8" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5275,7 +5275,7 @@
         <v>4</v>
       </c>
       <c r="W45" s="10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>7</v>
@@ -5332,20 +5332,20 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M46" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -5353,7 +5353,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O46" s="8" t="inlineStr">
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5437,20 +5437,20 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M47" s="7" t="n">
+      <c r="M47" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -5458,7 +5458,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O47" s="8" t="inlineStr">
+      <c r="O47" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5485,7 +5485,7 @@
         <v>4</v>
       </c>
       <c r="W47" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X47" s="10" t="n">
         <v>7</v>
@@ -5542,20 +5542,20 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M48" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -5563,7 +5563,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O48" s="8" t="inlineStr">
+      <c r="O48" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5647,20 +5647,20 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M49" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -5668,7 +5668,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O49" s="8" t="inlineStr">
+      <c r="O49" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5748,20 +5748,20 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M50" s="7" t="n">
+      <c r="M50" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -5769,7 +5769,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O50" s="8" t="inlineStr">
+      <c r="O50" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5853,20 +5853,20 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="8" t="inlineStr">
+        <v>-9</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M51" s="7" t="n">
+      <c r="M51" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5874,7 +5874,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O51" s="8" t="inlineStr">
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5954,20 +5954,20 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M52" s="7" t="n">
+      <c r="M52" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5975,7 +5975,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O52" s="8" t="inlineStr">
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6059,20 +6059,20 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L53" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M53" s="7" t="n">
+      <c r="M53" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -6080,7 +6080,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O53" s="8" t="inlineStr">
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6092,7 +6092,7 @@
         <v>2</v>
       </c>
       <c r="R53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" s="9" t="n">
         <v>1</v>
@@ -6100,8 +6100,8 @@
       <c r="T53" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U53" s="9" t="n">
-        <v>0</v>
+      <c r="U53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V53" s="9" t="n">
         <v>3</v>
@@ -6164,20 +6164,20 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M54" s="7" t="n">
+      <c r="M54" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -6185,7 +6185,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O54" s="8" t="inlineStr">
+      <c r="O54" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6269,20 +6269,20 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M55" s="7" t="n">
+      <c r="M55" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -6290,7 +6290,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O55" s="8" t="inlineStr">
+      <c r="O55" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6314,7 +6314,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6374,20 +6374,20 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L56" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M56" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M56" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -6395,7 +6395,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O56" s="8" t="inlineStr">
+      <c r="O56" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6416,13 +6416,13 @@
         <v>1</v>
       </c>
       <c r="U56" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V56" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="V56" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>7</v>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6475,20 +6475,20 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>56</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M57" s="7" t="n">
+      <c r="M57" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -6496,7 +6496,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O57" s="8" t="inlineStr">
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6519,11 +6519,11 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>0</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>5</v>
@@ -6531,8 +6531,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -6580,20 +6580,20 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M58" s="7" t="n">
+      <c r="M58" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -6601,7 +6601,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O58" s="8" t="inlineStr">
+      <c r="O58" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6681,20 +6681,20 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M59" s="7" t="n">
+      <c r="M59" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -6702,7 +6702,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O59" s="8" t="inlineStr">
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6786,20 +6786,20 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M60" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M60" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -6807,7 +6807,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O60" s="8" t="inlineStr">
+      <c r="O60" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6891,20 +6891,20 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M61" s="7" t="n">
+      <c r="M61" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6912,7 +6912,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O61" s="8" t="inlineStr">
+      <c r="O61" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6938,8 +6938,8 @@
       <c r="V61" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W61" s="9" t="n">
-        <v>1</v>
+      <c r="W61" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>7</v>
@@ -6996,20 +6996,20 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M62" s="7" t="n">
+      <c r="M62" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -7017,7 +7017,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O62" s="8" t="inlineStr">
+      <c r="O62" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7101,20 +7101,20 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M63" s="7" t="n">
+      <c r="M63" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -7122,7 +7122,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O63" s="8" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7202,20 +7202,20 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M64" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M64" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -7223,13 +7223,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O64" s="8" t="inlineStr">
+      <c r="O64" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>1</v>
@@ -7250,7 +7250,7 @@
         <v>4</v>
       </c>
       <c r="W64" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X64" s="10" t="n">
         <v>7</v>
@@ -7303,20 +7303,20 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M65" s="7" t="n">
+      <c r="M65" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -7324,7 +7324,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O65" s="8" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7404,20 +7404,20 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M66" s="7" t="n">
+      <c r="M66" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -7425,7 +7425,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O66" s="8" t="inlineStr">
+      <c r="O66" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7449,7 +7449,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7513,12 +7513,12 @@
       <c r="K67" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L67" s="8" t="inlineStr">
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M67" s="7" t="n">
+      <c r="M67" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -7526,7 +7526,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O67" s="8" t="inlineStr">
+      <c r="O67" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7606,20 +7606,20 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M68" s="7" t="n">
+      <c r="M68" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -7627,7 +7627,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O68" s="8" t="inlineStr">
+      <c r="O68" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7651,7 +7651,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7707,20 +7707,20 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M69" s="7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M69" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -7728,7 +7728,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O69" s="8" t="inlineStr">
+      <c r="O69" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7794,7 +7794,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7808,20 +7808,20 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M70" s="7" t="n">
+      <c r="M70" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -7829,7 +7829,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O70" s="8" t="inlineStr">
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7846,14 +7846,14 @@
       <c r="S70" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T70" s="9" t="n">
-        <v>0</v>
+      <c r="T70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7913,20 +7913,20 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L71" s="8" t="inlineStr">
+        <v>-12</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M71" s="7" t="n">
+      <c r="M71" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -7934,7 +7934,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O71" s="8" t="inlineStr">
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8014,20 +8014,20 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M72" s="7" t="n">
+      <c r="M72" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -8035,7 +8035,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O72" s="8" t="inlineStr">
+      <c r="O72" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8115,20 +8115,20 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L73" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M73" s="7" t="n">
+      <c r="M73" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -8136,7 +8136,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O73" s="8" t="inlineStr">
+      <c r="O73" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8216,20 +8216,20 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M74" s="7" t="n">
+      <c r="M74" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -8237,7 +8237,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O74" s="8" t="inlineStr">
+      <c r="O74" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8260,11 +8260,11 @@
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" s="9" t="n">
-        <v>0</v>
+      <c r="V74" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W74" s="10" t="n">
+        <v>19</v>
       </c>
       <c r="X74" s="10" t="n">
         <v>6</v>
@@ -8321,20 +8321,20 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="8" t="inlineStr">
+        <v>-12</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M75" s="7" t="n">
+      <c r="M75" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -8342,7 +8342,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O75" s="8" t="inlineStr">
+      <c r="O75" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8422,20 +8422,20 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M76" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M76" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -8443,7 +8443,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O76" s="8" t="inlineStr">
+      <c r="O76" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8466,11 +8466,11 @@
       <c r="U76" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W76" s="9" t="n">
-        <v>0</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>6</v>
@@ -8527,20 +8527,20 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M77" s="7" t="n">
+      <c r="M77" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -8548,7 +8548,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O77" s="8" t="inlineStr">
+      <c r="O77" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8572,7 +8572,7 @@
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8628,20 +8628,20 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M78" s="7" t="n">
+      <c r="M78" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
@@ -8649,7 +8649,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O78" s="8" t="inlineStr">
+      <c r="O78" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8729,20 +8729,20 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M79" s="7" t="n">
+      <c r="M79" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -8750,7 +8750,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O79" s="8" t="inlineStr">
+      <c r="O79" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8777,7 +8777,7 @@
         <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X79" s="10" t="n">
         <v>7</v>
@@ -8830,20 +8830,20 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M80" s="7" t="n">
+      <c r="M80" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -8851,7 +8851,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O80" s="8" t="inlineStr">
+      <c r="O80" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8935,20 +8935,20 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M81" s="7" t="n">
+      <c r="M81" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -8956,7 +8956,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O81" s="8" t="inlineStr">
+      <c r="O81" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9040,20 +9040,20 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M82" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M82" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
@@ -9061,7 +9061,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O82" s="8" t="inlineStr">
+      <c r="O82" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9145,20 +9145,20 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M83" s="7" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M83" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -9166,7 +9166,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O83" s="8" t="inlineStr">
+      <c r="O83" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9258,12 +9258,12 @@
       <c r="K84" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L84" s="8" t="inlineStr">
+      <c r="L84" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M84" s="7" t="n">
+      <c r="M84" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
@@ -9271,7 +9271,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O84" s="8" t="inlineStr">
+      <c r="O84" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9295,7 +9295,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9337,7 +9337,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9351,20 +9351,20 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M85" s="7" t="n">
+      <c r="M85" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -9372,7 +9372,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O85" s="8" t="inlineStr">
+      <c r="O85" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9392,8 +9392,8 @@
       <c r="T85" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U85" s="9" t="n">
-        <v>0</v>
+      <c r="U85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V85" s="9" t="n">
         <v>3</v>
@@ -9442,7 +9442,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9456,20 +9456,20 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M86" s="7" t="n">
+      <c r="M86" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
@@ -9477,7 +9477,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O86" s="8" t="inlineStr">
+      <c r="O86" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9497,8 +9497,8 @@
       <c r="T86" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U86" s="9" t="n">
-        <v>0</v>
+      <c r="U86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V86" s="10" t="n">
         <v>4</v>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9561,20 +9561,20 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M87" s="7" t="n">
+      <c r="M87" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -9582,7 +9582,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O87" s="8" t="inlineStr">
+      <c r="O87" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9597,7 +9597,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" s="10" t="n">
         <v>1</v>
@@ -9608,8 +9608,8 @@
       <c r="V87" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W87" s="9" t="n">
-        <v>2</v>
+      <c r="W87" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>7</v>
@@ -9666,20 +9666,20 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M88" s="7" t="n">
+      <c r="M88" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
@@ -9687,7 +9687,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O88" s="8" t="inlineStr">
+      <c r="O88" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9711,7 +9711,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9771,20 +9771,20 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M89" s="7" t="n">
+      <c r="M89" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -9792,7 +9792,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O89" s="8" t="inlineStr">
+      <c r="O89" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9876,20 +9876,20 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M90" s="7" t="n">
+      <c r="M90" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -9897,7 +9897,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O90" s="8" t="inlineStr">
+      <c r="O90" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9977,20 +9977,20 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M91" s="7" t="n">
+      <c r="M91" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -9998,7 +9998,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O91" s="8" t="inlineStr">
+      <c r="O91" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10078,20 +10078,20 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M92" s="7" t="n">
+      <c r="M92" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -10099,7 +10099,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O92" s="8" t="inlineStr">
+      <c r="O92" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10179,20 +10179,20 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M93" s="7" t="n">
+      <c r="M93" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -10200,13 +10200,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O93" s="8" t="inlineStr">
+      <c r="O93" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" s="9" t="n">
         <v>0</v>
@@ -10224,7 +10224,7 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -10266,7 +10266,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10280,20 +10280,20 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M94" s="7" t="n">
+      <c r="M94" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
@@ -10301,7 +10301,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O94" s="8" t="inlineStr">
+      <c r="O94" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10318,8 +10318,8 @@
       <c r="S94" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T94" s="9" t="n">
-        <v>0</v>
+      <c r="T94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U94" s="9" t="n">
         <v>0</v>
@@ -10385,20 +10385,20 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M95" s="7" t="n">
+      <c r="M95" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -10406,7 +10406,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O95" s="8" t="inlineStr">
+      <c r="O95" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10498,12 +10498,12 @@
       <c r="K96" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L96" s="8" t="inlineStr">
+      <c r="L96" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M96" s="7" t="n">
+      <c r="M96" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
@@ -10511,7 +10511,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O96" s="8" t="inlineStr">
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10591,20 +10591,20 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M97" s="7" t="n">
+      <c r="M97" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -10612,7 +10612,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O97" s="8" t="inlineStr">
+      <c r="O97" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10696,20 +10696,20 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L98" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M98" s="7" t="n">
+      <c r="M98" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
@@ -10717,7 +10717,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O98" s="8" t="inlineStr">
+      <c r="O98" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10797,20 +10797,20 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M99" s="7" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M99" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -10818,7 +10818,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O99" s="8" t="inlineStr">
+      <c r="O99" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10898,20 +10898,20 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M100" s="7" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M100" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
@@ -10919,7 +10919,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O100" s="8" t="inlineStr">
+      <c r="O100" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10985,7 +10985,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10999,35 +10999,35 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M101" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O101" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P101" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L101" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M101" s="7" t="n">
-        <v>46387</v>
-      </c>
-      <c r="N101" s="4" t="inlineStr">
-        <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O101" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P101" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="Q101" s="9" t="n">
         <v>1</v>
       </c>
@@ -11040,8 +11040,8 @@
       <c r="T101" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U101" s="9" t="n">
-        <v>0</v>
+      <c r="U101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V101" s="9" t="n">
         <v>2</v>
@@ -11100,20 +11100,20 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M102" s="7" t="n">
+      <c r="M102" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
@@ -11121,7 +11121,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O102" s="8" t="inlineStr">
+      <c r="O102" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11201,20 +11201,20 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M103" s="7" t="n">
+      <c r="M103" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -11222,7 +11222,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O103" s="8" t="inlineStr">
+      <c r="O103" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11302,20 +11302,20 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L104" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M104" s="7" t="n">
+      <c r="M104" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -11323,7 +11323,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O104" s="8" t="inlineStr">
+      <c r="O104" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11403,20 +11403,20 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M105" s="7" t="n">
+      <c r="M105" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N105" s="4" t="inlineStr">
@@ -11424,7 +11424,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O105" s="8" t="inlineStr">
+      <c r="O105" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11448,7 +11448,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11504,20 +11504,20 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M106" s="7" t="n">
+      <c r="M106" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N106" s="4" t="inlineStr">
@@ -11525,13 +11525,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O106" s="8" t="inlineStr">
+      <c r="O106" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q106" s="9" t="n">
         <v>0</v>
@@ -11546,7 +11546,7 @@
         <v>1</v>
       </c>
       <c r="U106" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V106" s="10" t="n">
         <v>4</v>
@@ -11609,20 +11609,20 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M107" s="7" t="n">
+      <c r="M107" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N107" s="4" t="inlineStr">
@@ -11630,7 +11630,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O107" s="8" t="inlineStr">
+      <c r="O107" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11710,20 +11710,20 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L108" s="8" t="inlineStr">
+        <v>-14</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M108" s="7" t="n">
+      <c r="M108" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N108" s="4" t="inlineStr">
@@ -11731,7 +11731,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O108" s="8" t="inlineStr">
+      <c r="O108" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11815,20 +11815,20 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M109" s="7" t="n">
+      <c r="M109" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N109" s="4" t="inlineStr">
@@ -11836,7 +11836,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O109" s="8" t="inlineStr">
+      <c r="O109" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11916,20 +11916,20 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M110" s="7" t="n">
+      <c r="M110" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N110" s="4" t="inlineStr">
@@ -11937,7 +11937,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O110" s="8" t="inlineStr">
+      <c r="O110" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12017,20 +12017,20 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M111" s="7" t="n">
+      <c r="M111" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N111" s="4" t="inlineStr">
@@ -12038,7 +12038,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O111" s="8" t="inlineStr">
+      <c r="O111" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12061,11 +12061,11 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>3</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X111" s="10" t="n">
         <v>7</v>
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12122,20 +12122,20 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M112" s="7" t="n">
+      <c r="M112" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N112" s="4" t="inlineStr">
@@ -12143,7 +12143,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O112" s="8" t="inlineStr">
+      <c r="O112" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12166,11 +12166,11 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>0</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>7</v>
@@ -12223,20 +12223,20 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L113" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M113" s="7" t="n">
+      <c r="M113" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N113" s="4" t="inlineStr">
@@ -12244,7 +12244,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O113" s="8" t="inlineStr">
+      <c r="O113" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12324,20 +12324,20 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M114" s="7" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M114" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N114" s="4" t="inlineStr">
@@ -12345,7 +12345,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O114" s="8" t="inlineStr">
+      <c r="O114" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12425,20 +12425,20 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M115" s="7" t="n">
+      <c r="M115" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N115" s="4" t="inlineStr">
@@ -12446,7 +12446,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O115" s="8" t="inlineStr">
+      <c r="O115" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12470,7 +12470,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12530,20 +12530,20 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M116" s="7" t="n">
+      <c r="M116" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N116" s="4" t="inlineStr">
@@ -12551,7 +12551,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O116" s="8" t="inlineStr">
+      <c r="O116" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12700,7 +12700,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -12718,7 +12718,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -12784,7 +12784,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -12799,7 +12799,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -12817,7 +12817,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>2.29</v>
+        <v>2.71</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -12832,7 +12832,7 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -12850,7 +12850,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3.33</v>
+        <v>3.67</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -12865,7 +12865,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -12883,7 +12883,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -12898,7 +12898,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -12916,7 +12916,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -12949,7 +12949,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -12964,7 +12964,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -12982,7 +12982,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -12997,7 +12997,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -13030,7 +13030,7 @@
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -13048,7 +13048,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13081,13 +13081,13 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -13096,7 +13096,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -13114,7 +13114,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -13129,7 +13129,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -13162,7 +13162,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -13180,7 +13180,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13195,7 +13195,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -13213,13 +13213,13 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
         <v>2</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -13228,7 +13228,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -13294,7 +13294,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -13312,7 +13312,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -13378,7 +13378,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13426,7 +13426,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -13444,7 +13444,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -13510,7 +13510,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
         <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/105/inyear.xlsx
+++ b/docs/d/105/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/105/inyear.xlsx
+++ b/docs/d/105/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/105/inyear.xlsx
+++ b/docs/d/105/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/105/inyear.xlsx
+++ b/docs/d/105/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/105/inyear.xlsx
+++ b/docs/d/105/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 36 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1218,8 +1218,8 @@
       <c r="T5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U5" s="9" t="n">
-        <v>0</v>
+      <c r="U5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V5" s="9" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1532,8 +1532,8 @@
       <c r="U8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="9" t="n">
-        <v>3</v>
+      <c r="V8" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1633,8 +1633,8 @@
       <c r="U9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="9" t="n">
-        <v>3</v>
+      <c r="V9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="P14" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q14" s="9" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" s="10" t="n">
         <v>1</v>
@@ -2819,13 +2819,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-17</v>
+        <v>-15</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>4</v>
       </c>
       <c r="W21" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X21" s="10" t="n">
         <v>7</v>
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3442,8 +3442,8 @@
       <c r="P27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" s="9" t="n">
-        <v>0</v>
+      <c r="Q27" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3809,13 +3809,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3850,14 +3850,14 @@
       <c r="T31" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U31" s="9" t="n">
-        <v>0</v>
+      <c r="U31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V31" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W31" s="9" t="n">
-        <v>3</v>
+      <c r="W31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>4</v>
@@ -3908,13 +3908,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" s="9" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
         <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>6</v>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="P42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42" s="9" t="n">
         <v>0</v>
@@ -5055,7 +5055,7 @@
         <v>1</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" s="9" t="n">
         <v>0</v>
@@ -5126,13 +5126,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>4</v>
       </c>
       <c r="W44" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X44" s="10" t="n">
         <v>6</v>
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -6164,13 +6164,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -6996,13 +6996,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7202,13 +7202,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         </is>
       </c>
       <c r="P87" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q87" s="10" t="n">
         <v>2</v>
@@ -10280,13 +10280,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -10797,13 +10797,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-20</v>
+        <v>-17</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -11504,13 +11504,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>4</v>
       </c>
       <c r="W106" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X106" s="10" t="n">
         <v>7</v>
@@ -11815,13 +11815,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>1</v>
@@ -11860,7 +11860,7 @@
         <v>1</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -12425,13 +12425,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12685,7 +12685,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -12718,7 +12718,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -12850,13 +12850,13 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -12883,7 +12883,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>

--- a/docs/d/105/inyear.xlsx
+++ b/docs/d/105/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 36 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="9" t="n">
         <v>1</v>
@@ -898,13 +898,13 @@
         <v>0</v>
       </c>
       <c r="S2" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="T2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V2" s="9" t="n">
         <v>2</v>
@@ -1383,13 +1383,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" s="9" t="n">
         <v>0</v>
@@ -2720,13 +2720,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>1</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="9" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2819,13 +2819,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2866,8 +2866,8 @@
       <c r="V21" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W21" s="9" t="n">
-        <v>3</v>
+      <c r="W21" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X21" s="10" t="n">
         <v>7</v>
@@ -3146,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" s="9" t="n">
         <v>0</v>
@@ -3218,10 +3218,10 @@
         <v>8</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3512,13 +3512,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3844,8 +3844,8 @@
       <c r="R31" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S31" s="9" t="n">
-        <v>1</v>
+      <c r="S31" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T31" s="10" t="n">
         <v>1</v>
@@ -5437,13 +5437,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="P50" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q50" s="9" t="n">
         <v>1</v>
@@ -6269,13 +6269,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6891,13 +6891,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="P61" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q61" s="10" t="n">
         <v>2</v>
@@ -6939,7 +6939,7 @@
         <v>4</v>
       </c>
       <c r="W61" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>7</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="P68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q68" s="9" t="n">
         <v>0</v>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>0</v>
@@ -8115,13 +8115,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8422,13 +8422,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9288,8 +9288,8 @@
       <c r="S84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T84" s="9" t="n">
-        <v>0</v>
+      <c r="T84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U84" s="9" t="n">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10223,11 +10223,11 @@
       <c r="U93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V93" s="9" t="n">
-        <v>3</v>
+      <c r="V93" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W93" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>7</v>
@@ -10985,7 +10985,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10999,13 +10999,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11043,8 +11043,8 @@
       <c r="U101" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V101" s="9" t="n">
-        <v>2</v>
+      <c r="V101" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -12685,7 +12685,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -12817,7 +12817,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -12883,7 +12883,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -13279,7 +13279,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13378,7 +13378,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13444,7 +13444,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
